--- a/data/monkey.xlsx
+++ b/data/monkey.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ecosenza/s/DifussionCompass/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA293DFF-C4E2-ED45-9EAA-992F405BEB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C357A1-8BAB-2D45-A75F-3634C1E1471E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -758,9 +758,6 @@
     <t>Website / link (GitHub page or website)</t>
   </si>
   <si>
-    <t>https://github.com/scilus/versaFlow</t>
-  </si>
-  <si>
     <t>https://github.com/Washington-University/HCPpipelines</t>
   </si>
   <si>
@@ -906,13 +903,16 @@
   </si>
   <si>
     <t>No documented support identified in the comparison</t>
+  </si>
+  <si>
+    <t>https://github.com/AlexVCaron/versaFlow</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -992,6 +992,14 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1028,10 +1036,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1069,8 +1078,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3141,7 +3154,7 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" ht="30" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8" ht="32" x14ac:dyDescent="0.15">
       <c r="A76" s="10" t="s">
         <v>234</v>
       </c>
@@ -3149,22 +3162,22 @@
         <v>235</v>
       </c>
       <c r="C76" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D76" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="D76" s="11" t="s">
-        <v>241</v>
-      </c>
       <c r="E76" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="F76" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="G76" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="G76" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="H76" s="11" t="s">
-        <v>236</v>
+      <c r="H76" s="19" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.15">
@@ -3191,9 +3204,12 @@
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A18:H18"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H76" r:id="rId1" xr:uid="{14FB5754-1760-9040-ABC1-F7BF801E4687}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3210,16 +3226,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3230,10 +3246,10 @@
         <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3244,10 +3260,10 @@
         <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3258,10 +3274,10 @@
         <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3272,10 +3288,10 @@
         <v>34</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3286,10 +3302,10 @@
         <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3300,10 +3316,10 @@
         <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3314,10 +3330,10 @@
         <v>63</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3328,10 +3344,10 @@
         <v>66</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3342,10 +3358,10 @@
         <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3356,10 +3372,10 @@
         <v>70</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3370,10 +3386,10 @@
         <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3384,10 +3400,10 @@
         <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3398,10 +3414,10 @@
         <v>81</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3412,10 +3428,10 @@
         <v>83</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3426,10 +3442,10 @@
         <v>85</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3440,10 +3456,10 @@
         <v>110</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3454,10 +3470,10 @@
         <v>116</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3468,10 +3484,10 @@
         <v>122</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3482,10 +3498,10 @@
         <v>124</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3496,10 +3512,10 @@
         <v>126</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3510,10 +3526,10 @@
         <v>154</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3524,10 +3540,10 @@
         <v>156</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3538,10 +3554,10 @@
         <v>158</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3552,10 +3568,10 @@
         <v>160</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3566,10 +3582,10 @@
         <v>163</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3580,10 +3596,10 @@
         <v>165</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3594,10 +3610,10 @@
         <v>167</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3608,10 +3624,10 @@
         <v>172</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3622,10 +3638,10 @@
         <v>174</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3636,10 +3652,10 @@
         <v>176</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3650,10 +3666,10 @@
         <v>22</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3664,10 +3680,10 @@
         <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3678,10 +3694,10 @@
         <v>27</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3692,10 +3708,10 @@
         <v>145</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3706,10 +3722,10 @@
         <v>149</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3720,10 +3736,10 @@
         <v>235</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3734,10 +3750,10 @@
         <v>19</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3748,10 +3764,10 @@
         <v>36</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3762,10 +3778,10 @@
         <v>46</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3776,10 +3792,10 @@
         <v>56</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3790,10 +3806,10 @@
         <v>87</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3804,10 +3820,10 @@
         <v>95</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3818,10 +3834,10 @@
         <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3832,10 +3848,10 @@
         <v>112</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3846,10 +3862,10 @@
         <v>120</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3860,10 +3876,10 @@
         <v>128</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3874,10 +3890,10 @@
         <v>136</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3888,10 +3904,10 @@
         <v>147</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3902,10 +3918,10 @@
         <v>152</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3916,24 +3932,24 @@
         <v>169</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3944,10 +3960,10 @@
         <v>179</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3958,10 +3974,10 @@
         <v>181</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3972,10 +3988,10 @@
         <v>183</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3986,10 +4002,10 @@
         <v>118</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4000,10 +4016,10 @@
         <v>72</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4014,57 +4030,57 @@
         <v>74</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C61" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4072,13 +4088,13 @@
         <v>205</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="22.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4094,13 +4110,13 @@
         <v>221</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -4111,10 +4127,10 @@
         <v>218</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -4122,13 +4138,13 @@
         <v>223</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -4136,13 +4152,13 @@
         <v>225</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -4150,12 +4166,12 @@
         <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B71" s="1"/>
     </row>
@@ -4164,7 +4180,7 @@
         <v>20</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -4172,7 +4188,7 @@
         <v>64</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -4180,7 +4196,7 @@
         <v>23</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
